--- a/out/S03_employee_training_feedback/agent3/agent3_review.xlsx
+++ b/out/S03_employee_training_feedback/agent3/agent3_review.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -673,118 +673,50 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>FLOOR</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Text-pipe dependency</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
+          <t>FLOOR - lowest dimension. Never a sum or an average.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="4" t="n">
         <v>100</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>EXHAUSTIVE</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>EXECUTABLE</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Interaction</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="n">
+          <t>Tests Agent 4 could actually run</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>BOUNDED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>FLOOR</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>FLOOR - lowest dimension. Never a sum or an average.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>EXECUTABLE</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Tests Agent 4 could actually run</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>0% for every target and every survey. Block C cannot bind a canonical id to a LimeSurvey field without Agent 2's build manifest, which is not published yet. Logical and executable coverage are tracked separately precisely so this gap is visible.</t>
         </is>
@@ -801,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I323"/>
+  <dimension ref="A1:I298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14191,1131 +14123,6 @@
         </is>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" s="2" t="inlineStr">
-        <is>
-          <t>TC-f854bec903</t>
-        </is>
-      </c>
-      <c r="B299" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C299" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D299" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E299" s="2" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="F299" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G299" s="5" t="inlineStr">
-        <is>
-          <t>S1-O1</t>
-        </is>
-      </c>
-      <c r="H299" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I299" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="2" t="inlineStr">
-        <is>
-          <t>TC-f854bec903</t>
-        </is>
-      </c>
-      <c r="B300" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C300" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D300" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E300" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="F300" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G300" s="5" t="inlineStr">
-        <is>
-          <t>S2-O1</t>
-        </is>
-      </c>
-      <c r="H300" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I300" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="2" t="inlineStr">
-        <is>
-          <t>TC-f854bec903</t>
-        </is>
-      </c>
-      <c r="B301" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C301" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D301" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E301" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="F301" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G301" s="5" t="inlineStr">
-        <is>
-          <t>Q1-O1</t>
-        </is>
-      </c>
-      <c r="H301" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I301" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>TC-f854bec903</t>
-        </is>
-      </c>
-      <c r="B302" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C302" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D302" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E302" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="F302" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G302" s="5" t="inlineStr">
-        <is>
-          <t>Q2-O1</t>
-        </is>
-      </c>
-      <c r="H302" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I302" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>TC-f854bec903</t>
-        </is>
-      </c>
-      <c r="B303" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C303" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D303" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E303" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="F303" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G303" s="5" t="inlineStr">
-        <is>
-          <t>Q3-O1</t>
-        </is>
-      </c>
-      <c r="H303" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I303" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>TC-f854bec903</t>
-        </is>
-      </c>
-      <c r="B304" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C304" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D304" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E304" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="F304" s="2" t="inlineStr">
-        <is>
-          <t>multi</t>
-        </is>
-      </c>
-      <c r="G304" s="5" t="inlineStr">
-        <is>
-          <t>['Q4-O1']</t>
-        </is>
-      </c>
-      <c r="H304" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I304" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>TC-f854bec903</t>
-        </is>
-      </c>
-      <c r="B305" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C305" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D305" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E305" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="F305" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G305" s="5" t="inlineStr">
-        <is>
-          <t>Q5-O1</t>
-        </is>
-      </c>
-      <c r="H305" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I305" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="2" t="inlineStr">
-        <is>
-          <t>TC-f854bec903</t>
-        </is>
-      </c>
-      <c r="B306" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C306" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D306" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E306" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="F306" s="2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G306" s="5" t="inlineStr">
-        <is>
-          <t>xxxxxxxxxx</t>
-        </is>
-      </c>
-      <c r="H306" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I306" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="inlineStr">
-        <is>
-          <t>TC-4e572a11b8</t>
-        </is>
-      </c>
-      <c r="B307" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C307" s="2" t="inlineStr">
-        <is>
-          <t>DT1's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D307" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E307" s="2" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="F307" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G307" s="5" t="inlineStr">
-        <is>
-          <t>S1-O1</t>
-        </is>
-      </c>
-      <c r="H307" s="2" t="inlineStr">
-        <is>
-          <t>S1, DT1</t>
-        </is>
-      </c>
-      <c r="I307" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="inlineStr">
-        <is>
-          <t>TC-4e572a11b8</t>
-        </is>
-      </c>
-      <c r="B308" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C308" s="2" t="inlineStr">
-        <is>
-          <t>DT1's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D308" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E308" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="F308" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G308" s="5" t="inlineStr">
-        <is>
-          <t>S2-O1</t>
-        </is>
-      </c>
-      <c r="H308" s="2" t="inlineStr">
-        <is>
-          <t>S1, DT1</t>
-        </is>
-      </c>
-      <c r="I308" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="inlineStr">
-        <is>
-          <t>TC-e713ebe920</t>
-        </is>
-      </c>
-      <c r="B309" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C309" s="2" t="inlineStr">
-        <is>
-          <t>Q1's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D309" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E309" s="2" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="F309" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G309" s="5" t="inlineStr">
-        <is>
-          <t>S1-O1</t>
-        </is>
-      </c>
-      <c r="H309" s="2" t="inlineStr">
-        <is>
-          <t>S1, Q1</t>
-        </is>
-      </c>
-      <c r="I309" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="inlineStr">
-        <is>
-          <t>TC-e713ebe920</t>
-        </is>
-      </c>
-      <c r="B310" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C310" s="2" t="inlineStr">
-        <is>
-          <t>Q1's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D310" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E310" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="F310" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G310" s="5" t="inlineStr">
-        <is>
-          <t>S2-O1</t>
-        </is>
-      </c>
-      <c r="H310" s="2" t="inlineStr">
-        <is>
-          <t>S1, Q1</t>
-        </is>
-      </c>
-      <c r="I310" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="inlineStr">
-        <is>
-          <t>TC-e713ebe920</t>
-        </is>
-      </c>
-      <c r="B311" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C311" s="2" t="inlineStr">
-        <is>
-          <t>Q1's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D311" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E311" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="F311" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G311" s="5" t="inlineStr">
-        <is>
-          <t>Q1-O1</t>
-        </is>
-      </c>
-      <c r="H311" s="2" t="inlineStr">
-        <is>
-          <t>S1, Q1</t>
-        </is>
-      </c>
-      <c r="I311" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2" t="inlineStr">
-        <is>
-          <t>TC-d2c8555f25</t>
-        </is>
-      </c>
-      <c r="B312" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C312" s="2" t="inlineStr">
-        <is>
-          <t>Q2's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D312" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E312" s="2" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="F312" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G312" s="5" t="inlineStr">
-        <is>
-          <t>S1-O1</t>
-        </is>
-      </c>
-      <c r="H312" s="2" t="inlineStr">
-        <is>
-          <t>S1, Q2</t>
-        </is>
-      </c>
-      <c r="I312" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="inlineStr">
-        <is>
-          <t>TC-d2c8555f25</t>
-        </is>
-      </c>
-      <c r="B313" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C313" s="2" t="inlineStr">
-        <is>
-          <t>Q2's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D313" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E313" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="F313" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G313" s="5" t="inlineStr">
-        <is>
-          <t>S2-O1</t>
-        </is>
-      </c>
-      <c r="H313" s="2" t="inlineStr">
-        <is>
-          <t>S1, Q2</t>
-        </is>
-      </c>
-      <c r="I313" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="inlineStr">
-        <is>
-          <t>TC-d2c8555f25</t>
-        </is>
-      </c>
-      <c r="B314" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C314" s="2" t="inlineStr">
-        <is>
-          <t>Q2's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D314" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E314" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="F314" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G314" s="5" t="inlineStr">
-        <is>
-          <t>Q1-O1</t>
-        </is>
-      </c>
-      <c r="H314" s="2" t="inlineStr">
-        <is>
-          <t>S1, Q2</t>
-        </is>
-      </c>
-      <c r="I314" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="inlineStr">
-        <is>
-          <t>TC-d2c8555f25</t>
-        </is>
-      </c>
-      <c r="B315" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C315" s="2" t="inlineStr">
-        <is>
-          <t>Q2's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D315" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E315" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="F315" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G315" s="5" t="inlineStr">
-        <is>
-          <t>Q2-O1</t>
-        </is>
-      </c>
-      <c r="H315" s="2" t="inlineStr">
-        <is>
-          <t>S1, Q2</t>
-        </is>
-      </c>
-      <c r="I315" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="inlineStr">
-        <is>
-          <t>TC-23513b235e</t>
-        </is>
-      </c>
-      <c r="B316" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C316" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D316" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E316" s="2" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="F316" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G316" s="5" t="inlineStr">
-        <is>
-          <t>S1-O1</t>
-        </is>
-      </c>
-      <c r="H316" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I316" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="inlineStr">
-        <is>
-          <t>TC-23513b235e</t>
-        </is>
-      </c>
-      <c r="B317" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C317" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D317" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E317" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="F317" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G317" s="5" t="inlineStr">
-        <is>
-          <t>S2-O1</t>
-        </is>
-      </c>
-      <c r="H317" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I317" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2" t="inlineStr">
-        <is>
-          <t>TC-23513b235e</t>
-        </is>
-      </c>
-      <c r="B318" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C318" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D318" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E318" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="F318" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G318" s="5" t="inlineStr">
-        <is>
-          <t>Q1-O1</t>
-        </is>
-      </c>
-      <c r="H318" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I318" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="inlineStr">
-        <is>
-          <t>TC-23513b235e</t>
-        </is>
-      </c>
-      <c r="B319" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C319" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D319" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E319" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="F319" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G319" s="5" t="inlineStr">
-        <is>
-          <t>Q2-O1</t>
-        </is>
-      </c>
-      <c r="H319" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I319" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="inlineStr">
-        <is>
-          <t>TC-23513b235e</t>
-        </is>
-      </c>
-      <c r="B320" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C320" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D320" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E320" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="F320" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G320" s="5" t="inlineStr">
-        <is>
-          <t>Q3-O1</t>
-        </is>
-      </c>
-      <c r="H320" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I320" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="2" t="inlineStr">
-        <is>
-          <t>TC-23513b235e</t>
-        </is>
-      </c>
-      <c r="B321" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C321" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D321" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E321" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="F321" s="2" t="inlineStr">
-        <is>
-          <t>multi</t>
-        </is>
-      </c>
-      <c r="G321" s="5" t="inlineStr">
-        <is>
-          <t>['Q4-O1']</t>
-        </is>
-      </c>
-      <c r="H321" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I321" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="inlineStr">
-        <is>
-          <t>TC-23513b235e</t>
-        </is>
-      </c>
-      <c r="B322" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C322" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D322" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E322" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="F322" s="2" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="G322" s="5" t="inlineStr">
-        <is>
-          <t>Q5-O1</t>
-        </is>
-      </c>
-      <c r="H322" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I322" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="2" t="inlineStr">
-        <is>
-          <t>TC-23513b235e</t>
-        </is>
-      </c>
-      <c r="B323" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C323" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D323" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E323" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="F323" s="2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G323" s="5" t="inlineStr">
-        <is>
-          <t>xxxxxxxxxx</t>
-        </is>
-      </c>
-      <c r="H323" s="2" t="inlineStr">
-        <is>
-          <t>Q5, Q6</t>
-        </is>
-      </c>
-      <c r="I323" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15327,7 +14134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16951,196 +15758,6 @@
       <c r="F53" s="2" t="inlineStr">
         <is>
           <t>the page must NOT advance; a required-answer message must appear against this question</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TC-f854bec903</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>wording_contains</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>the question text must render the answer given at Q5</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TC-4e572a11b8</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>wording_contains</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>DT1</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>the question text must render the answer given at S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TC-e713ebe920</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>wording_contains</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>the question text must render the answer given at S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TC-d2c8555f25</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>wording_contains</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>the question text must render the answer given at S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TC-23513b235e</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>question_visible</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>the question must appear, proving its show-condition</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TC-23513b235e</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>reflects_dependency</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>and must simultaneously reflect its dependency on Q5</t>
         </is>
       </c>
     </row>
@@ -17215,7 +15832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J408"/>
+  <dimension ref="A1:J374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17285,7 +15902,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>EX-eb4d84e697</t>
+          <t>EX-39f20b1ec3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -17335,7 +15952,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>EX-eb4d84e697</t>
+          <t>EX-39f20b1ec3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -17385,7 +16002,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>EX-eb4d84e697</t>
+          <t>EX-39f20b1ec3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -17419,7 +16036,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>EX-eb4d84e697</t>
+          <t>EX-39f20b1ec3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -17469,7 +16086,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>EX-eb4d84e697</t>
+          <t>EX-39f20b1ec3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -17519,7 +16136,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EX-eb4d84e697</t>
+          <t>EX-39f20b1ec3</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -17569,7 +16186,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EX-eb4d84e697</t>
+          <t>EX-39f20b1ec3</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -17619,7 +16236,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EX-eb4d84e697</t>
+          <t>EX-39f20b1ec3</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -17669,7 +16286,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>EX-eb4d84e697</t>
+          <t>EX-39f20b1ec3</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -17719,7 +16336,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>EX-eb4d84e697</t>
+          <t>EX-39f20b1ec3</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -17769,7 +16386,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EX-eb4d84e697</t>
+          <t>EX-39f20b1ec3</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -17803,7 +16420,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EX-733f08ff16</t>
+          <t>EX-1c8f4d8cab</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -17853,7 +16470,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EX-733f08ff16</t>
+          <t>EX-1c8f4d8cab</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -17903,7 +16520,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EX-733f08ff16</t>
+          <t>EX-1c8f4d8cab</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -17937,7 +16554,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>EX-733f08ff16</t>
+          <t>EX-1c8f4d8cab</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -17987,7 +16604,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EX-733f08ff16</t>
+          <t>EX-1c8f4d8cab</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -18037,7 +16654,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>EX-733f08ff16</t>
+          <t>EX-1c8f4d8cab</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -18087,7 +16704,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EX-733f08ff16</t>
+          <t>EX-1c8f4d8cab</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -18137,7 +16754,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EX-733f08ff16</t>
+          <t>EX-1c8f4d8cab</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -18187,7 +16804,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>EX-733f08ff16</t>
+          <t>EX-1c8f4d8cab</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -18237,7 +16854,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>EX-733f08ff16</t>
+          <t>EX-1c8f4d8cab</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -18287,7 +16904,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>EX-733f08ff16</t>
+          <t>EX-1c8f4d8cab</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -18321,7 +16938,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>EX-21f1ffa902</t>
+          <t>EX-50d54b86ed</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -18371,7 +16988,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>EX-21f1ffa902</t>
+          <t>EX-50d54b86ed</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -18421,7 +17038,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>EX-21f1ffa902</t>
+          <t>EX-50d54b86ed</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -18455,7 +17072,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>EX-21f1ffa902</t>
+          <t>EX-50d54b86ed</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -18505,7 +17122,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>EX-21f1ffa902</t>
+          <t>EX-50d54b86ed</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -18555,7 +17172,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>EX-21f1ffa902</t>
+          <t>EX-50d54b86ed</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -18605,7 +17222,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>EX-21f1ffa902</t>
+          <t>EX-50d54b86ed</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -18655,7 +17272,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>EX-21f1ffa902</t>
+          <t>EX-50d54b86ed</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -18705,7 +17322,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>EX-21f1ffa902</t>
+          <t>EX-50d54b86ed</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -18755,7 +17372,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>EX-21f1ffa902</t>
+          <t>EX-50d54b86ed</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -18805,7 +17422,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>EX-21f1ffa902</t>
+          <t>EX-50d54b86ed</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -18839,7 +17456,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EX-28ccc6076a</t>
+          <t>EX-76d6c052ea</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -18889,7 +17506,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>EX-28ccc6076a</t>
+          <t>EX-76d6c052ea</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -18939,7 +17556,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EX-28ccc6076a</t>
+          <t>EX-76d6c052ea</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -18973,7 +17590,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>EX-28ccc6076a</t>
+          <t>EX-76d6c052ea</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -19023,7 +17640,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>EX-28ccc6076a</t>
+          <t>EX-76d6c052ea</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -19073,7 +17690,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>EX-28ccc6076a</t>
+          <t>EX-76d6c052ea</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -19123,7 +17740,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>EX-28ccc6076a</t>
+          <t>EX-76d6c052ea</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -19173,7 +17790,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>EX-28ccc6076a</t>
+          <t>EX-76d6c052ea</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -19223,7 +17840,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>EX-28ccc6076a</t>
+          <t>EX-76d6c052ea</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -19273,7 +17890,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>EX-28ccc6076a</t>
+          <t>EX-76d6c052ea</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -19323,7 +17940,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>EX-28ccc6076a</t>
+          <t>EX-76d6c052ea</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -19357,7 +17974,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EX-083c6f1e76</t>
+          <t>EX-0dbd1697bd</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -19407,7 +18024,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>EX-083c6f1e76</t>
+          <t>EX-0dbd1697bd</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -19457,7 +18074,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>EX-083c6f1e76</t>
+          <t>EX-0dbd1697bd</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -19491,7 +18108,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>EX-083c6f1e76</t>
+          <t>EX-0dbd1697bd</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -19541,7 +18158,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>EX-083c6f1e76</t>
+          <t>EX-0dbd1697bd</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -19591,7 +18208,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>EX-083c6f1e76</t>
+          <t>EX-0dbd1697bd</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -19641,7 +18258,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>EX-083c6f1e76</t>
+          <t>EX-0dbd1697bd</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -19691,7 +18308,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>EX-083c6f1e76</t>
+          <t>EX-0dbd1697bd</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -19741,7 +18358,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>EX-083c6f1e76</t>
+          <t>EX-0dbd1697bd</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -19791,7 +18408,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>EX-083c6f1e76</t>
+          <t>EX-0dbd1697bd</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -19841,7 +18458,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>EX-083c6f1e76</t>
+          <t>EX-0dbd1697bd</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -19875,7 +18492,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>EX-8fdfddb190</t>
+          <t>EX-27fc7321ff</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -19925,7 +18542,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>EX-8fdfddb190</t>
+          <t>EX-27fc7321ff</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -19975,7 +18592,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>EX-8fdfddb190</t>
+          <t>EX-27fc7321ff</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -20009,7 +18626,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>EX-8fdfddb190</t>
+          <t>EX-27fc7321ff</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -20059,7 +18676,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>EX-8fdfddb190</t>
+          <t>EX-27fc7321ff</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -20109,7 +18726,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>EX-8fdfddb190</t>
+          <t>EX-27fc7321ff</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -20159,7 +18776,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>EX-8fdfddb190</t>
+          <t>EX-27fc7321ff</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -20209,7 +18826,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>EX-8fdfddb190</t>
+          <t>EX-27fc7321ff</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -20259,7 +18876,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>EX-8fdfddb190</t>
+          <t>EX-27fc7321ff</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -20309,7 +18926,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>EX-8fdfddb190</t>
+          <t>EX-27fc7321ff</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -20359,7 +18976,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>EX-8fdfddb190</t>
+          <t>EX-27fc7321ff</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -20393,7 +19010,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>EX-d8f9b3254d</t>
+          <t>EX-a75ec7bba2</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -20443,7 +19060,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>EX-d8f9b3254d</t>
+          <t>EX-a75ec7bba2</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -20493,7 +19110,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>EX-d8f9b3254d</t>
+          <t>EX-a75ec7bba2</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -20527,7 +19144,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>EX-d8f9b3254d</t>
+          <t>EX-a75ec7bba2</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -20577,7 +19194,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>EX-d8f9b3254d</t>
+          <t>EX-a75ec7bba2</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -20627,7 +19244,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>EX-d8f9b3254d</t>
+          <t>EX-a75ec7bba2</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -20677,7 +19294,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>EX-d8f9b3254d</t>
+          <t>EX-a75ec7bba2</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -20727,7 +19344,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>EX-d8f9b3254d</t>
+          <t>EX-a75ec7bba2</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -20777,7 +19394,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>EX-d8f9b3254d</t>
+          <t>EX-a75ec7bba2</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -20827,7 +19444,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>EX-d8f9b3254d</t>
+          <t>EX-a75ec7bba2</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -20877,7 +19494,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>EX-d8f9b3254d</t>
+          <t>EX-a75ec7bba2</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -20911,7 +19528,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>EX-92926dccbb</t>
+          <t>EX-71dbf15fb1</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -20961,7 +19578,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>EX-92926dccbb</t>
+          <t>EX-71dbf15fb1</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -21011,7 +19628,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>EX-92926dccbb</t>
+          <t>EX-71dbf15fb1</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -21045,7 +19662,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>EX-92926dccbb</t>
+          <t>EX-71dbf15fb1</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -21095,7 +19712,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>EX-92926dccbb</t>
+          <t>EX-71dbf15fb1</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -21145,7 +19762,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>EX-92926dccbb</t>
+          <t>EX-71dbf15fb1</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -21195,7 +19812,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>EX-92926dccbb</t>
+          <t>EX-71dbf15fb1</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -21245,7 +19862,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>EX-92926dccbb</t>
+          <t>EX-71dbf15fb1</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -21295,7 +19912,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>EX-92926dccbb</t>
+          <t>EX-71dbf15fb1</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -21329,7 +19946,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>EX-f892a59729</t>
+          <t>EX-f9530cea73</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -21379,7 +19996,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>EX-f892a59729</t>
+          <t>EX-f9530cea73</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -21429,7 +20046,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>EX-f892a59729</t>
+          <t>EX-f9530cea73</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -21463,7 +20080,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>EX-f892a59729</t>
+          <t>EX-f9530cea73</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -21513,7 +20130,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>EX-f892a59729</t>
+          <t>EX-f9530cea73</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -21563,7 +20180,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>EX-f892a59729</t>
+          <t>EX-f9530cea73</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -21613,7 +20230,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>EX-f892a59729</t>
+          <t>EX-f9530cea73</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -21663,7 +20280,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>EX-f892a59729</t>
+          <t>EX-f9530cea73</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -21713,7 +20330,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>EX-f892a59729</t>
+          <t>EX-f9530cea73</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -21763,7 +20380,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>EX-f892a59729</t>
+          <t>EX-f9530cea73</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -21797,7 +20414,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>EX-98cfa67ce0</t>
+          <t>EX-f04b5c1897</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -21847,7 +20464,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>EX-98cfa67ce0</t>
+          <t>EX-f04b5c1897</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -21897,7 +20514,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>EX-98cfa67ce0</t>
+          <t>EX-f04b5c1897</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -21931,7 +20548,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>EX-98cfa67ce0</t>
+          <t>EX-f04b5c1897</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -21981,7 +20598,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>EX-98cfa67ce0</t>
+          <t>EX-f04b5c1897</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -22031,7 +20648,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>EX-98cfa67ce0</t>
+          <t>EX-f04b5c1897</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -22081,7 +20698,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>EX-98cfa67ce0</t>
+          <t>EX-f04b5c1897</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -22131,7 +20748,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>EX-98cfa67ce0</t>
+          <t>EX-f04b5c1897</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -22181,7 +20798,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>EX-98cfa67ce0</t>
+          <t>EX-f04b5c1897</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -22231,7 +20848,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>EX-98cfa67ce0</t>
+          <t>EX-f04b5c1897</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -22281,7 +20898,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>EX-98cfa67ce0</t>
+          <t>EX-f04b5c1897</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -22315,7 +20932,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>EX-7113374fc5</t>
+          <t>EX-3f2ce37788</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -22365,7 +20982,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>EX-7113374fc5</t>
+          <t>EX-3f2ce37788</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -22415,7 +21032,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>EX-7113374fc5</t>
+          <t>EX-3f2ce37788</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -22449,7 +21066,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>EX-7113374fc5</t>
+          <t>EX-3f2ce37788</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -22499,7 +21116,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>EX-7113374fc5</t>
+          <t>EX-3f2ce37788</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -22549,7 +21166,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>EX-7113374fc5</t>
+          <t>EX-3f2ce37788</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -22599,7 +21216,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>EX-7113374fc5</t>
+          <t>EX-3f2ce37788</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -22649,7 +21266,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>EX-7113374fc5</t>
+          <t>EX-3f2ce37788</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -22699,7 +21316,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>EX-7113374fc5</t>
+          <t>EX-3f2ce37788</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -22749,7 +21366,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>EX-7113374fc5</t>
+          <t>EX-3f2ce37788</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -22799,7 +21416,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>EX-7113374fc5</t>
+          <t>EX-3f2ce37788</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -22833,7 +21450,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>EX-4894fb98c4</t>
+          <t>EX-b5e85af709</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -22883,7 +21500,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>EX-4894fb98c4</t>
+          <t>EX-b5e85af709</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -22933,7 +21550,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>EX-4894fb98c4</t>
+          <t>EX-b5e85af709</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -22967,7 +21584,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>EX-4894fb98c4</t>
+          <t>EX-b5e85af709</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -23017,7 +21634,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>EX-4894fb98c4</t>
+          <t>EX-b5e85af709</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -23067,7 +21684,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>EX-4894fb98c4</t>
+          <t>EX-b5e85af709</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -23117,7 +21734,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>EX-4894fb98c4</t>
+          <t>EX-b5e85af709</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -23167,7 +21784,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>EX-4894fb98c4</t>
+          <t>EX-b5e85af709</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -23217,7 +21834,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>EX-4894fb98c4</t>
+          <t>EX-b5e85af709</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -23251,7 +21868,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>EX-17feced8a2</t>
+          <t>EX-3b1939820e</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -23301,7 +21918,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>EX-17feced8a2</t>
+          <t>EX-3b1939820e</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -23351,7 +21968,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>EX-17feced8a2</t>
+          <t>EX-3b1939820e</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -23385,7 +22002,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>EX-17feced8a2</t>
+          <t>EX-3b1939820e</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -23435,7 +22052,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>EX-17feced8a2</t>
+          <t>EX-3b1939820e</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -23485,7 +22102,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>EX-17feced8a2</t>
+          <t>EX-3b1939820e</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -23535,7 +22152,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>EX-17feced8a2</t>
+          <t>EX-3b1939820e</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -23585,7 +22202,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>EX-17feced8a2</t>
+          <t>EX-3b1939820e</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -23635,7 +22252,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>EX-17feced8a2</t>
+          <t>EX-3b1939820e</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -23669,7 +22286,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>EX-02d7f3ee05</t>
+          <t>EX-69b5145940</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -23719,7 +22336,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>EX-02d7f3ee05</t>
+          <t>EX-69b5145940</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -23769,7 +22386,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>EX-02d7f3ee05</t>
+          <t>EX-69b5145940</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -23803,7 +22420,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>EX-02d7f3ee05</t>
+          <t>EX-69b5145940</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -23853,7 +22470,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>EX-02d7f3ee05</t>
+          <t>EX-69b5145940</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -23903,7 +22520,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>EX-02d7f3ee05</t>
+          <t>EX-69b5145940</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -23953,7 +22570,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>EX-02d7f3ee05</t>
+          <t>EX-69b5145940</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -24003,7 +22620,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>EX-02d7f3ee05</t>
+          <t>EX-69b5145940</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -24053,7 +22670,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>EX-02d7f3ee05</t>
+          <t>EX-69b5145940</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -24103,7 +22720,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>EX-02d7f3ee05</t>
+          <t>EX-69b5145940</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -24153,7 +22770,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>EX-02d7f3ee05</t>
+          <t>EX-69b5145940</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -24187,7 +22804,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>EX-cf0e76d6a1</t>
+          <t>EX-015e47b709</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -24237,7 +22854,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>EX-cf0e76d6a1</t>
+          <t>EX-015e47b709</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -24287,7 +22904,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>EX-cf0e76d6a1</t>
+          <t>EX-015e47b709</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -24321,7 +22938,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>EX-cf0e76d6a1</t>
+          <t>EX-015e47b709</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -24371,7 +22988,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>EX-cf0e76d6a1</t>
+          <t>EX-015e47b709</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -24421,7 +23038,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>EX-cf0e76d6a1</t>
+          <t>EX-015e47b709</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -24471,7 +23088,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>EX-cf0e76d6a1</t>
+          <t>EX-015e47b709</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -24521,7 +23138,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>EX-cf0e76d6a1</t>
+          <t>EX-015e47b709</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -24571,7 +23188,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>EX-cf0e76d6a1</t>
+          <t>EX-015e47b709</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -24621,7 +23238,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>EX-cf0e76d6a1</t>
+          <t>EX-015e47b709</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -24671,7 +23288,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>EX-cf0e76d6a1</t>
+          <t>EX-015e47b709</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -24705,7 +23322,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>EX-d7fa6b696e</t>
+          <t>EX-1df639f72f</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -24755,7 +23372,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>EX-d7fa6b696e</t>
+          <t>EX-1df639f72f</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -24805,7 +23422,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>EX-d7fa6b696e</t>
+          <t>EX-1df639f72f</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -24839,7 +23456,7 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>EX-d7fa6b696e</t>
+          <t>EX-1df639f72f</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -24889,7 +23506,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>EX-d7fa6b696e</t>
+          <t>EX-1df639f72f</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -24939,7 +23556,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>EX-d7fa6b696e</t>
+          <t>EX-1df639f72f</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -24989,7 +23606,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>EX-d7fa6b696e</t>
+          <t>EX-1df639f72f</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -25039,7 +23656,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>EX-d7fa6b696e</t>
+          <t>EX-1df639f72f</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -25089,7 +23706,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>EX-d7fa6b696e</t>
+          <t>EX-1df639f72f</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -25139,7 +23756,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>EX-d7fa6b696e</t>
+          <t>EX-1df639f72f</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -25189,7 +23806,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>EX-d7fa6b696e</t>
+          <t>EX-1df639f72f</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -25223,7 +23840,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>EX-04b95cbe5c</t>
+          <t>EX-0eb1bb29bc</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -25273,7 +23890,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>EX-04b95cbe5c</t>
+          <t>EX-0eb1bb29bc</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -25307,7 +23924,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>EX-117d2b195e</t>
+          <t>EX-96f8836bd4</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -25357,7 +23974,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>EX-117d2b195e</t>
+          <t>EX-96f8836bd4</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -25407,7 +24024,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>EX-117d2b195e</t>
+          <t>EX-96f8836bd4</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -25441,7 +24058,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>EX-5031af9c67</t>
+          <t>EX-987717f0b0</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -25491,7 +24108,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>EX-5031af9c67</t>
+          <t>EX-987717f0b0</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -25541,7 +24158,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>EX-5031af9c67</t>
+          <t>EX-987717f0b0</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -25575,7 +24192,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>EX-5031af9c67</t>
+          <t>EX-987717f0b0</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -25625,7 +24242,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>EX-5031af9c67</t>
+          <t>EX-987717f0b0</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -25675,7 +24292,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>EX-5031af9c67</t>
+          <t>EX-987717f0b0</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -25725,7 +24342,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>EX-5031af9c67</t>
+          <t>EX-987717f0b0</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -25775,7 +24392,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>EX-5031af9c67</t>
+          <t>EX-987717f0b0</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -25809,7 +24426,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>EX-7f392237fe</t>
+          <t>EX-219eb352d8</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -25859,7 +24476,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>EX-7f392237fe</t>
+          <t>EX-219eb352d8</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -25909,7 +24526,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>EX-7f392237fe</t>
+          <t>EX-219eb352d8</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -25943,7 +24560,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>EX-7f392237fe</t>
+          <t>EX-219eb352d8</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -25993,7 +24610,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>EX-7f392237fe</t>
+          <t>EX-219eb352d8</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -26043,7 +24660,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>EX-7f392237fe</t>
+          <t>EX-219eb352d8</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -26093,7 +24710,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>EX-7f392237fe</t>
+          <t>EX-219eb352d8</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -26135,7 +24752,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>EX-7f392237fe</t>
+          <t>EX-219eb352d8</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -26169,7 +24786,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>EX-37a38688c1</t>
+          <t>EX-ed5aedbbe7</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -26219,7 +24836,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>EX-37a38688c1</t>
+          <t>EX-ed5aedbbe7</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -26269,7 +24886,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>EX-37a38688c1</t>
+          <t>EX-ed5aedbbe7</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -26303,7 +24920,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>EX-37a38688c1</t>
+          <t>EX-ed5aedbbe7</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -26353,7 +24970,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>EX-37a38688c1</t>
+          <t>EX-ed5aedbbe7</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -26403,7 +25020,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>EX-37a38688c1</t>
+          <t>EX-ed5aedbbe7</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -26453,7 +25070,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>EX-37a38688c1</t>
+          <t>EX-ed5aedbbe7</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -26503,7 +25120,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>EX-37a38688c1</t>
+          <t>EX-ed5aedbbe7</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -26553,7 +25170,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>EX-37a38688c1</t>
+          <t>EX-ed5aedbbe7</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -26603,7 +25220,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>EX-37a38688c1</t>
+          <t>EX-ed5aedbbe7</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -26637,7 +25254,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>EX-c853cad8da</t>
+          <t>EX-8efbea2c9e</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -26687,7 +25304,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>EX-c853cad8da</t>
+          <t>EX-8efbea2c9e</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -26737,7 +25354,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>EX-c853cad8da</t>
+          <t>EX-8efbea2c9e</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -26771,7 +25388,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>EX-c853cad8da</t>
+          <t>EX-8efbea2c9e</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -26821,7 +25438,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>EX-c853cad8da</t>
+          <t>EX-8efbea2c9e</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -26871,7 +25488,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>EX-c853cad8da</t>
+          <t>EX-8efbea2c9e</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -26921,7 +25538,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>EX-c853cad8da</t>
+          <t>EX-8efbea2c9e</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -26971,7 +25588,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>EX-c853cad8da</t>
+          <t>EX-8efbea2c9e</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -27021,7 +25638,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>EX-c853cad8da</t>
+          <t>EX-8efbea2c9e</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -27071,7 +25688,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>EX-c853cad8da</t>
+          <t>EX-8efbea2c9e</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -27105,7 +25722,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>EX-7364b00fe5</t>
+          <t>EX-07381ea9b5</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -27155,7 +25772,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>EX-7364b00fe5</t>
+          <t>EX-07381ea9b5</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -27205,7 +25822,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>EX-7364b00fe5</t>
+          <t>EX-07381ea9b5</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -27239,7 +25856,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>EX-7364b00fe5</t>
+          <t>EX-07381ea9b5</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -27289,7 +25906,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>EX-7364b00fe5</t>
+          <t>EX-07381ea9b5</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -27339,7 +25956,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>EX-7364b00fe5</t>
+          <t>EX-07381ea9b5</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -27389,7 +26006,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>EX-7364b00fe5</t>
+          <t>EX-07381ea9b5</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -27439,7 +26056,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>EX-7364b00fe5</t>
+          <t>EX-07381ea9b5</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -27489,7 +26106,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>EX-7364b00fe5</t>
+          <t>EX-07381ea9b5</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -27539,7 +26156,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>EX-7364b00fe5</t>
+          <t>EX-07381ea9b5</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -27573,7 +26190,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>EX-7873b1b959</t>
+          <t>EX-4e0a8f673c</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -27623,7 +26240,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>EX-7873b1b959</t>
+          <t>EX-4e0a8f673c</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -27673,7 +26290,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>EX-7873b1b959</t>
+          <t>EX-4e0a8f673c</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -27707,7 +26324,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>EX-7873b1b959</t>
+          <t>EX-4e0a8f673c</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -27757,7 +26374,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>EX-7873b1b959</t>
+          <t>EX-4e0a8f673c</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -27807,7 +26424,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>EX-7873b1b959</t>
+          <t>EX-4e0a8f673c</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -27857,7 +26474,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>EX-7873b1b959</t>
+          <t>EX-4e0a8f673c</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -27907,7 +26524,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>EX-7873b1b959</t>
+          <t>EX-4e0a8f673c</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -27957,7 +26574,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>EX-7873b1b959</t>
+          <t>EX-4e0a8f673c</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -28007,7 +26624,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>EX-7873b1b959</t>
+          <t>EX-4e0a8f673c</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -28041,7 +26658,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>EX-f50bdb7402</t>
+          <t>EX-d841d64404</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -28091,7 +26708,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>EX-f50bdb7402</t>
+          <t>EX-d841d64404</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -28141,7 +26758,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>EX-f50bdb7402</t>
+          <t>EX-d841d64404</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -28175,7 +26792,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>EX-f50bdb7402</t>
+          <t>EX-d841d64404</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -28225,7 +26842,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>EX-f50bdb7402</t>
+          <t>EX-d841d64404</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -28275,7 +26892,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>EX-f50bdb7402</t>
+          <t>EX-d841d64404</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -28325,7 +26942,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>EX-f50bdb7402</t>
+          <t>EX-d841d64404</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -28375,7 +26992,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>EX-f50bdb7402</t>
+          <t>EX-d841d64404</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -28425,7 +27042,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>EX-f50bdb7402</t>
+          <t>EX-d841d64404</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -28475,7 +27092,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>EX-f50bdb7402</t>
+          <t>EX-d841d64404</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -28525,7 +27142,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>EX-f50bdb7402</t>
+          <t>EX-d841d64404</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -28575,7 +27192,7 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>EX-f50bdb7402</t>
+          <t>EX-d841d64404</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -28609,7 +27226,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>EX-a08dcc4743</t>
+          <t>EX-64a365b0ec</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -28659,7 +27276,7 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>EX-a08dcc4743</t>
+          <t>EX-64a365b0ec</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -28709,7 +27326,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>EX-a08dcc4743</t>
+          <t>EX-64a365b0ec</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -28743,7 +27360,7 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>EX-a08dcc4743</t>
+          <t>EX-64a365b0ec</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -28793,7 +27410,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>EX-a08dcc4743</t>
+          <t>EX-64a365b0ec</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -28843,7 +27460,7 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>EX-a08dcc4743</t>
+          <t>EX-64a365b0ec</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -28893,7 +27510,7 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>EX-a08dcc4743</t>
+          <t>EX-64a365b0ec</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -28943,7 +27560,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>EX-a08dcc4743</t>
+          <t>EX-64a365b0ec</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -28993,7 +27610,7 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>EX-a08dcc4743</t>
+          <t>EX-64a365b0ec</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -29043,7 +27660,7 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>EX-a08dcc4743</t>
+          <t>EX-64a365b0ec</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -29093,7 +27710,7 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>EX-a08dcc4743</t>
+          <t>EX-64a365b0ec</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -29143,7 +27760,7 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>EX-a08dcc4743</t>
+          <t>EX-64a365b0ec</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -29177,7 +27794,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>EX-5be1e0b343</t>
+          <t>EX-d487b6af28</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -29227,7 +27844,7 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>EX-5be1e0b343</t>
+          <t>EX-d487b6af28</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -29277,7 +27894,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>EX-5be1e0b343</t>
+          <t>EX-d487b6af28</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -29311,7 +27928,7 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>EX-5be1e0b343</t>
+          <t>EX-d487b6af28</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -29361,7 +27978,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>EX-5be1e0b343</t>
+          <t>EX-d487b6af28</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -29411,7 +28028,7 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>EX-5be1e0b343</t>
+          <t>EX-d487b6af28</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -29461,7 +28078,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>EX-5be1e0b343</t>
+          <t>EX-d487b6af28</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -29511,7 +28128,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>EX-5be1e0b343</t>
+          <t>EX-d487b6af28</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -29561,7 +28178,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>EX-5be1e0b343</t>
+          <t>EX-d487b6af28</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -29611,7 +28228,7 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>EX-5be1e0b343</t>
+          <t>EX-d487b6af28</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -29661,7 +28278,7 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>EX-5be1e0b343</t>
+          <t>EX-d487b6af28</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -29711,7 +28328,7 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>EX-5be1e0b343</t>
+          <t>EX-d487b6af28</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -29745,7 +28362,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -29795,7 +28412,7 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -29845,7 +28462,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -29879,7 +28496,7 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -29929,7 +28546,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -29979,7 +28596,7 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -30029,7 +28646,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -30079,7 +28696,7 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -30129,7 +28746,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -30179,7 +28796,7 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
@@ -30229,7 +28846,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -30279,7 +28896,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -30313,7 +28930,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>EX-f47b396592</t>
+          <t>EX-3ac6802d1f</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -30363,7 +28980,7 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>EX-f47b396592</t>
+          <t>EX-3ac6802d1f</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
@@ -30413,7 +29030,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>EX-f47b396592</t>
+          <t>EX-3ac6802d1f</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -30447,7 +29064,7 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>EX-f47b396592</t>
+          <t>EX-3ac6802d1f</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
@@ -30493,7 +29110,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>EX-f47b396592</t>
+          <t>EX-3ac6802d1f</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -30527,7 +29144,7 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>EX-b692509f29</t>
+          <t>EX-eecd515cae</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
@@ -30577,7 +29194,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>EX-b692509f29</t>
+          <t>EX-eecd515cae</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -30627,7 +29244,7 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>EX-b692509f29</t>
+          <t>EX-eecd515cae</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -30661,7 +29278,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>EX-b692509f29</t>
+          <t>EX-eecd515cae</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -30711,7 +29328,7 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>EX-b692509f29</t>
+          <t>EX-eecd515cae</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -30757,7 +29374,7 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>EX-b692509f29</t>
+          <t>EX-eecd515cae</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -30791,7 +29408,7 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>EX-07a1ea3839</t>
+          <t>EX-57801679ab</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -30841,7 +29458,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>EX-07a1ea3839</t>
+          <t>EX-57801679ab</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -30891,7 +29508,7 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>EX-07a1ea3839</t>
+          <t>EX-57801679ab</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -30925,7 +29542,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>EX-07a1ea3839</t>
+          <t>EX-57801679ab</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -30975,7 +29592,7 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>EX-07a1ea3839</t>
+          <t>EX-57801679ab</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -31025,7 +29642,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>EX-07a1ea3839</t>
+          <t>EX-57801679ab</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -31071,7 +29688,7 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>EX-07a1ea3839</t>
+          <t>EX-57801679ab</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -31105,7 +29722,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>EX-646de90976</t>
+          <t>EX-c6e91bdda7</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -31155,7 +29772,7 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>EX-646de90976</t>
+          <t>EX-c6e91bdda7</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -31205,7 +29822,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>EX-646de90976</t>
+          <t>EX-c6e91bdda7</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -31239,7 +29856,7 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>EX-646de90976</t>
+          <t>EX-c6e91bdda7</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -31289,7 +29906,7 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>EX-646de90976</t>
+          <t>EX-c6e91bdda7</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -31339,7 +29956,7 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>EX-646de90976</t>
+          <t>EX-c6e91bdda7</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
@@ -31389,7 +30006,7 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>EX-646de90976</t>
+          <t>EX-c6e91bdda7</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -31431,7 +30048,7 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>EX-646de90976</t>
+          <t>EX-c6e91bdda7</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
@@ -31465,7 +30082,7 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>EX-2e9a17f934</t>
+          <t>EX-3a30ac15c0</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -31515,7 +30132,7 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>EX-2e9a17f934</t>
+          <t>EX-3a30ac15c0</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
@@ -31565,7 +30182,7 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>EX-2e9a17f934</t>
+          <t>EX-3a30ac15c0</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
@@ -31599,7 +30216,7 @@
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>EX-2e9a17f934</t>
+          <t>EX-3a30ac15c0</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
@@ -31649,7 +30266,7 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>EX-2e9a17f934</t>
+          <t>EX-3a30ac15c0</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
@@ -31699,7 +30316,7 @@
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>EX-2e9a17f934</t>
+          <t>EX-3a30ac15c0</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
@@ -31749,7 +30366,7 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>EX-2e9a17f934</t>
+          <t>EX-3a30ac15c0</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
@@ -31799,7 +30416,7 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>EX-2e9a17f934</t>
+          <t>EX-3a30ac15c0</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -31845,7 +30462,7 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>EX-2e9a17f934</t>
+          <t>EX-3a30ac15c0</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
@@ -31879,7 +30496,7 @@
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>EX-a453f6c8bf</t>
+          <t>EX-e97705799d</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
@@ -31929,7 +30546,7 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>EX-a453f6c8bf</t>
+          <t>EX-e97705799d</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
@@ -31979,7 +30596,7 @@
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>EX-a453f6c8bf</t>
+          <t>EX-e97705799d</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
@@ -32013,7 +30630,7 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>EX-a453f6c8bf</t>
+          <t>EX-e97705799d</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
@@ -32063,7 +30680,7 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>EX-a453f6c8bf</t>
+          <t>EX-e97705799d</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
@@ -32113,7 +30730,7 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>EX-a453f6c8bf</t>
+          <t>EX-e97705799d</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -32163,7 +30780,7 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>EX-a453f6c8bf</t>
+          <t>EX-e97705799d</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
@@ -32213,7 +30830,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>EX-a453f6c8bf</t>
+          <t>EX-e97705799d</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -32263,7 +30880,7 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>EX-a453f6c8bf</t>
+          <t>EX-e97705799d</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
@@ -32309,7 +30926,7 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>EX-a453f6c8bf</t>
+          <t>EX-e97705799d</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -32343,7 +30960,7 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>EX-e3224b4f05</t>
+          <t>EX-c1df9ed4d8</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -32393,7 +31010,7 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>EX-e3224b4f05</t>
+          <t>EX-c1df9ed4d8</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -32443,7 +31060,7 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>EX-e3224b4f05</t>
+          <t>EX-c1df9ed4d8</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -32477,7 +31094,7 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>EX-e3224b4f05</t>
+          <t>EX-c1df9ed4d8</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -32527,7 +31144,7 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>EX-e3224b4f05</t>
+          <t>EX-c1df9ed4d8</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -32577,7 +31194,7 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>EX-e3224b4f05</t>
+          <t>EX-c1df9ed4d8</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -32627,7 +31244,7 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>EX-e3224b4f05</t>
+          <t>EX-c1df9ed4d8</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
@@ -32677,7 +31294,7 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>EX-e3224b4f05</t>
+          <t>EX-c1df9ed4d8</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -32727,7 +31344,7 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>EX-e3224b4f05</t>
+          <t>EX-c1df9ed4d8</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -32777,7 +31394,7 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>EX-e3224b4f05</t>
+          <t>EX-c1df9ed4d8</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -32811,7 +31428,7 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>EX-d068b6c486</t>
+          <t>EX-b7ad1c3af0</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
@@ -32861,7 +31478,7 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>EX-d068b6c486</t>
+          <t>EX-b7ad1c3af0</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -32911,7 +31528,7 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>EX-d068b6c486</t>
+          <t>EX-b7ad1c3af0</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
@@ -32945,7 +31562,7 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>EX-d068b6c486</t>
+          <t>EX-b7ad1c3af0</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -32995,7 +31612,7 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>EX-d068b6c486</t>
+          <t>EX-b7ad1c3af0</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
@@ -33045,7 +31662,7 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>EX-d068b6c486</t>
+          <t>EX-b7ad1c3af0</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
@@ -33095,7 +31712,7 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>EX-d068b6c486</t>
+          <t>EX-b7ad1c3af0</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
@@ -33145,7 +31762,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>EX-d068b6c486</t>
+          <t>EX-b7ad1c3af0</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -33195,7 +31812,7 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>EX-d068b6c486</t>
+          <t>EX-b7ad1c3af0</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -33245,7 +31862,7 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>EX-d068b6c486</t>
+          <t>EX-b7ad1c3af0</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -33291,7 +31908,7 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>EX-d068b6c486</t>
+          <t>EX-b7ad1c3af0</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -33325,7 +31942,7 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>EX-c82e976e81</t>
+          <t>EX-b8bc4acfba</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -33375,7 +31992,7 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>EX-c82e976e81</t>
+          <t>EX-b8bc4acfba</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -33425,7 +32042,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>EX-c82e976e81</t>
+          <t>EX-b8bc4acfba</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -33459,7 +32076,7 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>EX-c82e976e81</t>
+          <t>EX-b8bc4acfba</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -33509,7 +32126,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>EX-c82e976e81</t>
+          <t>EX-b8bc4acfba</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -33559,7 +32176,7 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>EX-c82e976e81</t>
+          <t>EX-b8bc4acfba</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -33609,7 +32226,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>EX-c82e976e81</t>
+          <t>EX-b8bc4acfba</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -33659,7 +32276,7 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>EX-c82e976e81</t>
+          <t>EX-b8bc4acfba</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -33709,7 +32326,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>EX-c82e976e81</t>
+          <t>EX-b8bc4acfba</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -33759,7 +32376,7 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>EX-c82e976e81</t>
+          <t>EX-b8bc4acfba</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -33809,7 +32426,7 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>EX-c82e976e81</t>
+          <t>EX-b8bc4acfba</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -33855,7 +32472,7 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>EX-c82e976e81</t>
+          <t>EX-b8bc4acfba</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -33889,7 +32506,7 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>EX-b7a9f19f18</t>
+          <t>EX-32bde75528</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -33939,7 +32556,7 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>EX-b7a9f19f18</t>
+          <t>EX-32bde75528</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -33989,7 +32606,7 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>EX-b7a9f19f18</t>
+          <t>EX-32bde75528</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -34023,7 +32640,7 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>EX-b7a9f19f18</t>
+          <t>EX-32bde75528</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
@@ -34073,7 +32690,7 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>EX-b7a9f19f18</t>
+          <t>EX-32bde75528</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -34123,7 +32740,7 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>EX-b7a9f19f18</t>
+          <t>EX-32bde75528</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -34173,7 +32790,7 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>EX-b7a9f19f18</t>
+          <t>EX-32bde75528</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -34223,7 +32840,7 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>EX-b7a9f19f18</t>
+          <t>EX-32bde75528</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -34273,7 +32890,7 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>EX-b7a9f19f18</t>
+          <t>EX-32bde75528</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -34323,7 +32940,7 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>EX-b7a9f19f18</t>
+          <t>EX-32bde75528</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -34373,7 +32990,7 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>EX-b7a9f19f18</t>
+          <t>EX-32bde75528</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -34423,7 +33040,7 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>EX-b7a9f19f18</t>
+          <t>EX-32bde75528</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
@@ -34457,7 +33074,7 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>EX-69c6bd0330</t>
+          <t>EX-e7c071d73a</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -34503,7 +33120,7 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>EX-69c6bd0330</t>
+          <t>EX-e7c071d73a</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -34537,7 +33154,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>EX-43de22cd6d</t>
+          <t>EX-6394d37ac2</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -34587,7 +33204,7 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>EX-43de22cd6d</t>
+          <t>EX-6394d37ac2</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
@@ -34633,7 +33250,7 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>EX-43de22cd6d</t>
+          <t>EX-6394d37ac2</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -34661,1562 +33278,6 @@
       <c r="J374" s="2" t="inlineStr">
         <is>
           <t>submit — the survey should REFUSE to move on, because S2 is not acceptable as answered</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" s="2" t="inlineStr">
-        <is>
-          <t>EX-dea613830d</t>
-        </is>
-      </c>
-      <c r="B375" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C375" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D375" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E375" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F375" s="5" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="G375" s="5" t="inlineStr">
-        <is>
-          <t>900001X100X1000</t>
-        </is>
-      </c>
-      <c r="H375" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I375" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J375" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (Yes) on S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" s="2" t="inlineStr">
-        <is>
-          <t>EX-dea613830d</t>
-        </is>
-      </c>
-      <c r="B376" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C376" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D376" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E376" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F376" s="5" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="G376" s="5" t="inlineStr">
-        <is>
-          <t>900001X100X1001</t>
-        </is>
-      </c>
-      <c r="H376" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I376" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J376" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (Yes) on S2</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="2" t="inlineStr">
-        <is>
-          <t>EX-dea613830d</t>
-        </is>
-      </c>
-      <c r="B377" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C377" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D377" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E377" s="2" t="inlineStr">
-        <is>
-          <t>submit_page</t>
-        </is>
-      </c>
-      <c r="F377" s="5" t="inlineStr"/>
-      <c r="G377" s="5" t="inlineStr"/>
-      <c r="H377" s="5" t="n"/>
-      <c r="I377" s="2" t="inlineStr"/>
-      <c r="J377" s="2" t="inlineStr">
-        <is>
-          <t>submit the Screening page</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="2" t="inlineStr">
-        <is>
-          <t>EX-dea613830d</t>
-        </is>
-      </c>
-      <c r="B378" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C378" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D378" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E378" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F378" s="5" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="G378" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1003</t>
-        </is>
-      </c>
-      <c r="H378" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I378" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J378" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (In person) on Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="2" t="inlineStr">
-        <is>
-          <t>EX-dea613830d</t>
-        </is>
-      </c>
-      <c r="B379" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C379" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D379" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E379" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F379" s="5" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="G379" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1004</t>
-        </is>
-      </c>
-      <c r="H379" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I379" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J379" s="2" t="inlineStr">
-        <is>
-          <t>select 1 (Very poor) on Q2</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" s="2" t="inlineStr">
-        <is>
-          <t>EX-dea613830d</t>
-        </is>
-      </c>
-      <c r="B380" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C380" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D380" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E380" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F380" s="5" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="G380" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1005</t>
-        </is>
-      </c>
-      <c r="H380" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I380" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J380" s="2" t="inlineStr">
-        <is>
-          <t>select 1 (Very poor) on Q3</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" s="2" t="inlineStr">
-        <is>
-          <t>EX-dea613830d</t>
-        </is>
-      </c>
-      <c r="B381" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C381" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D381" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E381" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F381" s="5" t="inlineStr">
-        <is>
-          <t>Q4_SQ001</t>
-        </is>
-      </c>
-      <c r="G381" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1006SQ001</t>
-        </is>
-      </c>
-      <c r="H381" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I381" s="2" t="inlineStr">
-        <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="J381" s="2" t="inlineStr">
-        <is>
-          <t>tick Q4_SQ001 (Content relevance)</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" s="2" t="inlineStr">
-        <is>
-          <t>EX-dea613830d</t>
-        </is>
-      </c>
-      <c r="B382" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C382" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D382" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E382" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F382" s="5" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="G382" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1013</t>
-        </is>
-      </c>
-      <c r="H382" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I382" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J382" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (Yes) on Q5</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" s="2" t="inlineStr">
-        <is>
-          <t>EX-dea613830d</t>
-        </is>
-      </c>
-      <c r="B383" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C383" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D383" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E383" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F383" s="5" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="G383" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1014</t>
-        </is>
-      </c>
-      <c r="H383" s="5" t="inlineStr">
-        <is>
-          <t>xxxxxxxxxx</t>
-        </is>
-      </c>
-      <c r="I383" s="2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="J383" s="2" t="inlineStr">
-        <is>
-          <t>type 'xxxxxxxxxx' into Q6</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="2" t="inlineStr">
-        <is>
-          <t>EX-dea613830d</t>
-        </is>
-      </c>
-      <c r="B384" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C384" s="2" t="inlineStr">
-        <is>
-          <t>Q6's wording renders the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="D384" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E384" s="2" t="inlineStr">
-        <is>
-          <t>submit_page</t>
-        </is>
-      </c>
-      <c r="F384" s="5" t="inlineStr"/>
-      <c r="G384" s="5" t="inlineStr"/>
-      <c r="H384" s="5" t="n"/>
-      <c r="I384" s="2" t="inlineStr"/>
-      <c r="J384" s="2" t="inlineStr">
-        <is>
-          <t>submit the final page and observe the end screen</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" s="2" t="inlineStr">
-        <is>
-          <t>EX-7d0bb75c0d</t>
-        </is>
-      </c>
-      <c r="B385" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C385" s="2" t="inlineStr">
-        <is>
-          <t>DT1's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D385" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E385" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F385" s="5" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="G385" s="5" t="inlineStr">
-        <is>
-          <t>900001X100X1000</t>
-        </is>
-      </c>
-      <c r="H385" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I385" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J385" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (Yes) on S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" s="2" t="inlineStr">
-        <is>
-          <t>EX-7d0bb75c0d</t>
-        </is>
-      </c>
-      <c r="B386" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C386" s="2" t="inlineStr">
-        <is>
-          <t>DT1's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D386" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E386" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F386" s="5" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="G386" s="5" t="inlineStr">
-        <is>
-          <t>900001X100X1001</t>
-        </is>
-      </c>
-      <c r="H386" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I386" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J386" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (Yes) on S2</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" s="2" t="inlineStr">
-        <is>
-          <t>EX-7d0bb75c0d</t>
-        </is>
-      </c>
-      <c r="B387" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C387" s="2" t="inlineStr">
-        <is>
-          <t>DT1's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D387" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E387" s="2" t="inlineStr">
-        <is>
-          <t>submit_page</t>
-        </is>
-      </c>
-      <c r="F387" s="5" t="inlineStr"/>
-      <c r="G387" s="5" t="inlineStr"/>
-      <c r="H387" s="5" t="n"/>
-      <c r="I387" s="2" t="inlineStr"/>
-      <c r="J387" s="2" t="inlineStr">
-        <is>
-          <t>submit the final page and observe the end screen</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="2" t="inlineStr">
-        <is>
-          <t>EX-4096e479c3</t>
-        </is>
-      </c>
-      <c r="B388" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C388" s="2" t="inlineStr">
-        <is>
-          <t>Q1's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D388" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E388" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F388" s="5" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="G388" s="5" t="inlineStr">
-        <is>
-          <t>900001X100X1000</t>
-        </is>
-      </c>
-      <c r="H388" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I388" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J388" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (Yes) on S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" s="2" t="inlineStr">
-        <is>
-          <t>EX-4096e479c3</t>
-        </is>
-      </c>
-      <c r="B389" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C389" s="2" t="inlineStr">
-        <is>
-          <t>Q1's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D389" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E389" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F389" s="5" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="G389" s="5" t="inlineStr">
-        <is>
-          <t>900001X100X1001</t>
-        </is>
-      </c>
-      <c r="H389" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I389" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J389" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (Yes) on S2</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" s="2" t="inlineStr">
-        <is>
-          <t>EX-4096e479c3</t>
-        </is>
-      </c>
-      <c r="B390" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C390" s="2" t="inlineStr">
-        <is>
-          <t>Q1's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D390" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E390" s="2" t="inlineStr">
-        <is>
-          <t>submit_page</t>
-        </is>
-      </c>
-      <c r="F390" s="5" t="inlineStr"/>
-      <c r="G390" s="5" t="inlineStr"/>
-      <c r="H390" s="5" t="n"/>
-      <c r="I390" s="2" t="inlineStr"/>
-      <c r="J390" s="2" t="inlineStr">
-        <is>
-          <t>submit the Screening page</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" s="2" t="inlineStr">
-        <is>
-          <t>EX-4096e479c3</t>
-        </is>
-      </c>
-      <c r="B391" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C391" s="2" t="inlineStr">
-        <is>
-          <t>Q1's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D391" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E391" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F391" s="5" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="G391" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1003</t>
-        </is>
-      </c>
-      <c r="H391" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I391" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J391" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (In person) on Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" s="2" t="inlineStr">
-        <is>
-          <t>EX-4096e479c3</t>
-        </is>
-      </c>
-      <c r="B392" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C392" s="2" t="inlineStr">
-        <is>
-          <t>Q1's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D392" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E392" s="2" t="inlineStr">
-        <is>
-          <t>submit_page</t>
-        </is>
-      </c>
-      <c r="F392" s="5" t="inlineStr"/>
-      <c r="G392" s="5" t="inlineStr"/>
-      <c r="H392" s="5" t="n"/>
-      <c r="I392" s="2" t="inlineStr"/>
-      <c r="J392" s="2" t="inlineStr">
-        <is>
-          <t>submit the final page and observe the end screen</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" s="2" t="inlineStr">
-        <is>
-          <t>EX-8f86a35ed2</t>
-        </is>
-      </c>
-      <c r="B393" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C393" s="2" t="inlineStr">
-        <is>
-          <t>Q2's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D393" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E393" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F393" s="5" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="G393" s="5" t="inlineStr">
-        <is>
-          <t>900001X100X1000</t>
-        </is>
-      </c>
-      <c r="H393" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I393" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J393" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (Yes) on S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" s="2" t="inlineStr">
-        <is>
-          <t>EX-8f86a35ed2</t>
-        </is>
-      </c>
-      <c r="B394" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C394" s="2" t="inlineStr">
-        <is>
-          <t>Q2's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D394" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E394" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F394" s="5" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="G394" s="5" t="inlineStr">
-        <is>
-          <t>900001X100X1001</t>
-        </is>
-      </c>
-      <c r="H394" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I394" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J394" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (Yes) on S2</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" s="2" t="inlineStr">
-        <is>
-          <t>EX-8f86a35ed2</t>
-        </is>
-      </c>
-      <c r="B395" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C395" s="2" t="inlineStr">
-        <is>
-          <t>Q2's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D395" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E395" s="2" t="inlineStr">
-        <is>
-          <t>submit_page</t>
-        </is>
-      </c>
-      <c r="F395" s="5" t="inlineStr"/>
-      <c r="G395" s="5" t="inlineStr"/>
-      <c r="H395" s="5" t="n"/>
-      <c r="I395" s="2" t="inlineStr"/>
-      <c r="J395" s="2" t="inlineStr">
-        <is>
-          <t>submit the Screening page</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" s="2" t="inlineStr">
-        <is>
-          <t>EX-8f86a35ed2</t>
-        </is>
-      </c>
-      <c r="B396" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C396" s="2" t="inlineStr">
-        <is>
-          <t>Q2's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D396" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E396" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F396" s="5" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="G396" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1003</t>
-        </is>
-      </c>
-      <c r="H396" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I396" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J396" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (In person) on Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" s="2" t="inlineStr">
-        <is>
-          <t>EX-8f86a35ed2</t>
-        </is>
-      </c>
-      <c r="B397" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C397" s="2" t="inlineStr">
-        <is>
-          <t>Q2's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D397" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E397" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F397" s="5" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="G397" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1004</t>
-        </is>
-      </c>
-      <c r="H397" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I397" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J397" s="2" t="inlineStr">
-        <is>
-          <t>select 1 (Very poor) on Q2</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" s="2" t="inlineStr">
-        <is>
-          <t>EX-8f86a35ed2</t>
-        </is>
-      </c>
-      <c r="B398" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C398" s="2" t="inlineStr">
-        <is>
-          <t>Q2's wording renders the answer given at S1</t>
-        </is>
-      </c>
-      <c r="D398" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E398" s="2" t="inlineStr">
-        <is>
-          <t>submit_page</t>
-        </is>
-      </c>
-      <c r="F398" s="5" t="inlineStr"/>
-      <c r="G398" s="5" t="inlineStr"/>
-      <c r="H398" s="5" t="n"/>
-      <c r="I398" s="2" t="inlineStr"/>
-      <c r="J398" s="2" t="inlineStr">
-        <is>
-          <t>submit the final page and observe the end screen</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" s="2" t="inlineStr">
-        <is>
-          <t>EX-53d3703483</t>
-        </is>
-      </c>
-      <c r="B399" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C399" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D399" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E399" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F399" s="5" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="G399" s="5" t="inlineStr">
-        <is>
-          <t>900001X100X1000</t>
-        </is>
-      </c>
-      <c r="H399" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I399" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J399" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (Yes) on S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" s="2" t="inlineStr">
-        <is>
-          <t>EX-53d3703483</t>
-        </is>
-      </c>
-      <c r="B400" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C400" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D400" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E400" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F400" s="5" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="G400" s="5" t="inlineStr">
-        <is>
-          <t>900001X100X1001</t>
-        </is>
-      </c>
-      <c r="H400" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I400" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J400" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (Yes) on S2</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" s="2" t="inlineStr">
-        <is>
-          <t>EX-53d3703483</t>
-        </is>
-      </c>
-      <c r="B401" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C401" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D401" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E401" s="2" t="inlineStr">
-        <is>
-          <t>submit_page</t>
-        </is>
-      </c>
-      <c r="F401" s="5" t="inlineStr"/>
-      <c r="G401" s="5" t="inlineStr"/>
-      <c r="H401" s="5" t="n"/>
-      <c r="I401" s="2" t="inlineStr"/>
-      <c r="J401" s="2" t="inlineStr">
-        <is>
-          <t>submit the Screening page</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" s="2" t="inlineStr">
-        <is>
-          <t>EX-53d3703483</t>
-        </is>
-      </c>
-      <c r="B402" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C402" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D402" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E402" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F402" s="5" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="G402" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1003</t>
-        </is>
-      </c>
-      <c r="H402" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I402" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J402" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (In person) on Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" s="2" t="inlineStr">
-        <is>
-          <t>EX-53d3703483</t>
-        </is>
-      </c>
-      <c r="B403" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C403" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D403" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E403" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F403" s="5" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="G403" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1004</t>
-        </is>
-      </c>
-      <c r="H403" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I403" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J403" s="2" t="inlineStr">
-        <is>
-          <t>select 1 (Very poor) on Q2</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="2" t="inlineStr">
-        <is>
-          <t>EX-53d3703483</t>
-        </is>
-      </c>
-      <c r="B404" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C404" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D404" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E404" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F404" s="5" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="G404" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1005</t>
-        </is>
-      </c>
-      <c r="H404" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I404" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J404" s="2" t="inlineStr">
-        <is>
-          <t>select 1 (Very poor) on Q3</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="2" t="inlineStr">
-        <is>
-          <t>EX-53d3703483</t>
-        </is>
-      </c>
-      <c r="B405" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C405" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D405" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E405" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F405" s="5" t="inlineStr">
-        <is>
-          <t>Q4_SQ001</t>
-        </is>
-      </c>
-      <c r="G405" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1006SQ001</t>
-        </is>
-      </c>
-      <c r="H405" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I405" s="2" t="inlineStr">
-        <is>
-          <t>checkbox</t>
-        </is>
-      </c>
-      <c r="J405" s="2" t="inlineStr">
-        <is>
-          <t>tick Q4_SQ001 (Content relevance)</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" s="2" t="inlineStr">
-        <is>
-          <t>EX-53d3703483</t>
-        </is>
-      </c>
-      <c r="B406" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C406" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D406" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E406" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F406" s="5" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="G406" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1013</t>
-        </is>
-      </c>
-      <c r="H406" s="5" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="I406" s="2" t="inlineStr">
-        <is>
-          <t>answer_code</t>
-        </is>
-      </c>
-      <c r="J406" s="2" t="inlineStr">
-        <is>
-          <t>select A001 (Yes) on Q5</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" s="2" t="inlineStr">
-        <is>
-          <t>EX-53d3703483</t>
-        </is>
-      </c>
-      <c r="B407" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C407" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D407" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E407" s="2" t="inlineStr">
-        <is>
-          <t>set_field</t>
-        </is>
-      </c>
-      <c r="F407" s="5" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="G407" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1014</t>
-        </is>
-      </c>
-      <c r="H407" s="5" t="inlineStr">
-        <is>
-          <t>xxxxxxxxxx</t>
-        </is>
-      </c>
-      <c r="I407" s="2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="J407" s="2" t="inlineStr">
-        <is>
-          <t>type 'xxxxxxxxxx' into Q6</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" s="2" t="inlineStr">
-        <is>
-          <t>EX-53d3703483</t>
-        </is>
-      </c>
-      <c r="B408" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C408" s="2" t="inlineStr">
-        <is>
-          <t>Q6 is shown by its guard and simultaneously reflects its dependency on Q5</t>
-        </is>
-      </c>
-      <c r="D408" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E408" s="2" t="inlineStr">
-        <is>
-          <t>submit_page</t>
-        </is>
-      </c>
-      <c r="F408" s="5" t="inlineStr"/>
-      <c r="G408" s="5" t="inlineStr"/>
-      <c r="H408" s="5" t="n"/>
-      <c r="I408" s="2" t="inlineStr"/>
-      <c r="J408" s="2" t="inlineStr">
-        <is>
-          <t>submit the final page and observe the end screen</t>
         </is>
       </c>
     </row>
@@ -36231,7 +33292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -36283,7 +33344,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>EX-eb4d84e697</t>
+          <t>EX-39f20b1ec3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -36320,7 +33381,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>EX-733f08ff16</t>
+          <t>EX-1c8f4d8cab</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -36355,7 +33416,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>EX-733f08ff16</t>
+          <t>EX-1c8f4d8cab</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -36392,7 +33453,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>EX-21f1ffa902</t>
+          <t>EX-50d54b86ed</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -36427,7 +33488,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>EX-21f1ffa902</t>
+          <t>EX-50d54b86ed</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -36464,7 +33525,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EX-28ccc6076a</t>
+          <t>EX-76d6c052ea</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -36499,7 +33560,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EX-28ccc6076a</t>
+          <t>EX-76d6c052ea</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -36536,7 +33597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EX-083c6f1e76</t>
+          <t>EX-0dbd1697bd</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -36571,7 +33632,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>EX-083c6f1e76</t>
+          <t>EX-0dbd1697bd</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -36608,7 +33669,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>EX-8fdfddb190</t>
+          <t>EX-27fc7321ff</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -36643,7 +33704,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EX-8fdfddb190</t>
+          <t>EX-27fc7321ff</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -36680,7 +33741,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EX-d8f9b3254d</t>
+          <t>EX-a75ec7bba2</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -36715,7 +33776,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EX-d8f9b3254d</t>
+          <t>EX-a75ec7bba2</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -36752,7 +33813,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EX-92926dccbb</t>
+          <t>EX-71dbf15fb1</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -36787,7 +33848,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>EX-92926dccbb</t>
+          <t>EX-71dbf15fb1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -36814,7 +33875,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EX-f892a59729</t>
+          <t>EX-f9530cea73</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -36849,7 +33910,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>EX-98cfa67ce0</t>
+          <t>EX-f04b5c1897</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -36884,7 +33945,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EX-98cfa67ce0</t>
+          <t>EX-f04b5c1897</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -36921,7 +33982,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EX-7113374fc5</t>
+          <t>EX-3f2ce37788</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -36956,7 +34017,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>EX-7113374fc5</t>
+          <t>EX-3f2ce37788</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -36983,7 +34044,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>EX-4894fb98c4</t>
+          <t>EX-b5e85af709</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -37020,7 +34081,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>EX-17feced8a2</t>
+          <t>EX-3b1939820e</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -37057,7 +34118,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>EX-02d7f3ee05</t>
+          <t>EX-69b5145940</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -37092,7 +34153,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>EX-02d7f3ee05</t>
+          <t>EX-69b5145940</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -37129,7 +34190,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>EX-cf0e76d6a1</t>
+          <t>EX-015e47b709</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -37164,7 +34225,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>EX-cf0e76d6a1</t>
+          <t>EX-015e47b709</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -37193,7 +34254,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>EX-d7fa6b696e</t>
+          <t>EX-1df639f72f</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -37220,7 +34281,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>EX-04b95cbe5c</t>
+          <t>EX-0eb1bb29bc</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -37251,7 +34312,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>EX-04b95cbe5c</t>
+          <t>EX-0eb1bb29bc</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -37280,7 +34341,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>EX-117d2b195e</t>
+          <t>EX-96f8836bd4</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -37311,7 +34372,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>EX-117d2b195e</t>
+          <t>EX-96f8836bd4</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -37340,7 +34401,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>EX-5031af9c67</t>
+          <t>EX-987717f0b0</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -37375,7 +34436,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>EX-7f392237fe</t>
+          <t>EX-219eb352d8</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -37410,7 +34471,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EX-7f392237fe</t>
+          <t>EX-219eb352d8</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -37445,7 +34506,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>EX-37a38688c1</t>
+          <t>EX-ed5aedbbe7</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -37480,7 +34541,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EX-c853cad8da</t>
+          <t>EX-8efbea2c9e</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -37515,7 +34576,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>EX-7364b00fe5</t>
+          <t>EX-07381ea9b5</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -37550,7 +34611,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>EX-7873b1b959</t>
+          <t>EX-4e0a8f673c</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -37585,7 +34646,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>EX-7873b1b959</t>
+          <t>EX-4e0a8f673c</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -37620,7 +34681,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>EX-f50bdb7402</t>
+          <t>EX-d841d64404</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -37655,7 +34716,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>EX-a08dcc4743</t>
+          <t>EX-64a365b0ec</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -37690,7 +34751,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>EX-5be1e0b343</t>
+          <t>EX-d487b6af28</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -37725,7 +34786,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -37760,7 +34821,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>EX-23e051535c</t>
+          <t>EX-c8e3b49a3c</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -37795,7 +34856,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EX-f47b396592</t>
+          <t>EX-3ac6802d1f</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -37830,7 +34891,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>EX-f47b396592</t>
+          <t>EX-3ac6802d1f</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -37865,7 +34926,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>EX-b692509f29</t>
+          <t>EX-eecd515cae</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -37900,7 +34961,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>EX-b692509f29</t>
+          <t>EX-eecd515cae</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -37935,7 +34996,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>EX-07a1ea3839</t>
+          <t>EX-57801679ab</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -37970,7 +35031,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>EX-07a1ea3839</t>
+          <t>EX-57801679ab</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -38005,7 +35066,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>EX-646de90976</t>
+          <t>EX-c6e91bdda7</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -38040,7 +35101,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>EX-646de90976</t>
+          <t>EX-c6e91bdda7</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -38075,7 +35136,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>EX-2e9a17f934</t>
+          <t>EX-3a30ac15c0</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -38110,7 +35171,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>EX-2e9a17f934</t>
+          <t>EX-3a30ac15c0</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -38145,7 +35206,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>EX-a453f6c8bf</t>
+          <t>EX-e97705799d</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -38180,7 +35241,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>EX-a453f6c8bf</t>
+          <t>EX-e97705799d</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -38215,7 +35276,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>EX-e3224b4f05</t>
+          <t>EX-c1df9ed4d8</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -38250,7 +35311,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>EX-e3224b4f05</t>
+          <t>EX-c1df9ed4d8</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -38285,7 +35346,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>EX-d068b6c486</t>
+          <t>EX-b7ad1c3af0</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -38320,7 +35381,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>EX-d068b6c486</t>
+          <t>EX-b7ad1c3af0</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -38355,7 +35416,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>EX-c82e976e81</t>
+          <t>EX-b8bc4acfba</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -38390,7 +35451,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>EX-b7a9f19f18</t>
+          <t>EX-32bde75528</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -38425,7 +35486,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>EX-69c6bd0330</t>
+          <t>EX-e7c071d73a</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -38460,7 +35521,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>EX-69c6bd0330</t>
+          <t>EX-e7c071d73a</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -38495,7 +35556,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>EX-43de22cd6d</t>
+          <t>EX-6394d37ac2</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -38530,7 +35591,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>EX-43de22cd6d</t>
+          <t>EX-6394d37ac2</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -38559,218 +35620,6 @@
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>LimeSurvey redisplays the page with the message against the offending question</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>EX-dea613830d</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>question_text_contains</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1014</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>the question text must render the answer given at Q5</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>EX-7d0bb75c0d</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>question_text_contains</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr"/>
-      <c r="E69" s="5" t="inlineStr"/>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>the question text must render the answer given at S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>EX-4096e479c3</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>question_text_contains</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1003</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>the question text must render the answer given at S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>EX-8f86a35ed2</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>question_text_contains</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1004</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>the question text must render the answer given at S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>EX-53d3703483</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>field_present</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1014</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>the question must appear, proving its show-condition</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>EX-53d3703483</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>question_text_contains</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>900001X101X1014</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>and must simultaneously reflect its dependency on Q5</t>
         </is>
       </c>
     </row>
@@ -38949,7 +35798,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
     </row>
@@ -38961,7 +35810,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>{"D1": 15, "D2": 3, "D3": 10, "D4": 12, "D5": 0, "D6": 4, "D7": 0, "D8": 0, "D9": 1}</t>
+          <t>{"D1": 15, "D2": 3, "D3": 10, "D4": 12, "D5": 0, "D6": 0, "D7": 0, "D8": 0, "D9": 0}</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
@@ -38973,7 +35822,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
     </row>
@@ -38984,7 +35833,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
     </row>
@@ -38995,7 +35844,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
     </row>
@@ -39030,7 +35879,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
